--- a/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/MINI BANDEJA DISMAY.xlsx
+++ b/LISTAS_ORDENADAS/MI/Mangueras Espatulas y Articulos de goma/MINI BANDEJA DISMAY.xlsx
@@ -747,14 +747,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="28" t="n">
-        <v>45208.55637228522</v>
+        <v>45266</v>
       </c>
       <c r="E1" s="4" t="n"/>
     </row>
-    <row r="2"/>
-    <row r="3"/>
-    <row r="4"/>
-    <row r="5"/>
     <row r="6" ht="22.5" customHeight="1" s="17">
       <c r="A6" s="2" t="inlineStr">
         <is>
@@ -803,16 +799,6 @@
       <c r="C12" s="39" t="n"/>
       <c r="D12" s="39" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
     <row r="23">
       <c r="C23" s="19" t="n"/>
     </row>
@@ -871,7 +857,6 @@
         <v>141</v>
       </c>
     </row>
-    <row r="30"/>
     <row r="31" ht="19.5" customHeight="1" s="17">
       <c r="A31" t="inlineStr">
         <is>
@@ -885,11 +870,10 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+          <t> </t>
+        </is>
+      </c>
+    </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
@@ -909,17 +893,12 @@
     </row>
     <row r="37" ht="16.5" customHeight="1" s="17"/>
     <row r="38" ht="16.5" customHeight="1" s="17"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42" ht="19.5" customHeight="1" s="17">
       <c r="A42" s="7" t="n"/>
     </row>
-    <row r="43"/>
     <row r="44">
       <c r="A44" s="5" t="n"/>
     </row>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="6" t="n"/>
     </row>
